--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1902.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1902.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83195BEA-2E15-43C4-80F4-D7711F3C1E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B7B3E9-0140-43A0-9EF3-638826AC954F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="65715" yWindow="795" windowWidth="48540" windowHeight="19755" activeTab="1" xr2:uid="{03F30607-691D-4B51-B95D-D1B19B24CEA7}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{03F30607-691D-4B51-B95D-D1B19B24CEA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="208">
   <si>
     <t>губ</t>
   </si>
@@ -476,9 +476,6 @@
   </si>
   <si>
     <t xml:space="preserve">Херсонская </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Г Николаевъ   </t>
   </si>
   <si>
     <t xml:space="preserve">Г Одесса  </t>
@@ -765,9 +762,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -805,7 +802,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -911,7 +908,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1053,7 +1050,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1883,7 +1880,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B75" s="2">
         <v>39.1</v>
@@ -2251,86 +2248,86 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="M1" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="Q1" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="U1" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="Y1" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Z1" s="9"/>
       <c r="AA1" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB1" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.55000000000000004">
@@ -2815,7 +2812,7 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" s="3">
         <v>128113</v>
@@ -4543,7 +4540,7 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B25" s="3">
         <v>45278</v>
@@ -6751,7 +6748,7 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>97</v>
@@ -8575,7 +8572,7 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="B67" s="10">
         <v>50867</v>
@@ -8671,7 +8668,7 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B68" s="3">
         <v>112419</v>
@@ -8767,7 +8764,7 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B69" s="3">
         <v>78259</v>
@@ -8863,7 +8860,7 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B70" s="10">
         <v>4291977</v>
@@ -8959,7 +8956,7 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B71" s="3">
         <v>114489</v>
@@ -9055,7 +9052,7 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B72" s="10">
         <v>6985484</v>
@@ -9151,7 +9148,7 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B73" s="3">
         <v>145918</v>
@@ -9247,7 +9244,7 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B74" s="3">
         <v>5924</v>
@@ -9343,7 +9340,7 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>97</v>
@@ -9439,7 +9436,7 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B76" s="3">
         <v>12115</v>
@@ -9535,7 +9532,7 @@
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B77" s="3">
         <v>86041</v>
@@ -9631,7 +9628,7 @@
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>97</v>
@@ -9727,7 +9724,7 @@
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B79" s="3">
         <v>24504</v>
@@ -9823,7 +9820,7 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B80" s="3">
         <v>70654</v>
@@ -10015,7 +10012,7 @@
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B82" s="3">
         <v>29270</v>
@@ -10207,7 +10204,7 @@
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B84" s="3">
         <v>547293</v>
@@ -10407,7 +10404,7 @@
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B86" s="3">
         <v>37109</v>
@@ -10503,7 +10500,7 @@
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>97</v>
@@ -10599,7 +10596,7 @@
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B88" s="3">
         <v>31154</v>
@@ -10791,7 +10788,7 @@
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>97</v>
@@ -10887,7 +10884,7 @@
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B91" s="3">
         <v>72854</v>
@@ -11079,7 +11076,7 @@
     </row>
     <row r="93" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B93" s="3">
         <v>0</v>
@@ -11175,7 +11172,7 @@
     </row>
     <row r="94" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B94" s="3">
         <v>239578</v>
@@ -11282,7 +11279,7 @@
     </row>
     <row r="95" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B95" s="3">
         <v>49779</v>
@@ -11378,7 +11375,7 @@
     </row>
     <row r="96" spans="1:36" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>97</v>
@@ -11474,7 +11471,7 @@
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>97</v>
@@ -11568,7 +11565,7 @@
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B98" s="3">
         <v>25387</v>
@@ -11664,7 +11661,7 @@
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B99" s="10">
         <v>34760</v>
@@ -11760,7 +11757,7 @@
     </row>
     <row r="100" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>97</v>
@@ -12142,7 +12139,7 @@
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B104" s="10">
         <v>151526</v>
@@ -12246,7 +12243,7 @@
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B105" s="3">
         <v>938391</v>
@@ -12350,7 +12347,7 @@
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B106" s="3">
         <v>7933875</v>
@@ -16299,30 +16296,36 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1902.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1902.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B7B3E9-0140-43A0-9EF3-638826AC954F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275B133C-539D-4362-9A9B-3BDA2C20E891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{03F30607-691D-4B51-B95D-D1B19B24CEA7}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="209">
   <si>
     <t>губ</t>
   </si>
@@ -662,6 +662,9 @@
   </si>
   <si>
     <t>чу YY</t>
+  </si>
+  <si>
+    <t>Строки для Одессы и Николаева переставлены местами</t>
   </si>
 </sst>
 </file>
@@ -726,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -744,6 +747,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8378,7 +8382,7 @@
         <v>82631</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>145</v>
       </c>
@@ -8474,8 +8478,8 @@
         <v>62903</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" t="s">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="11" t="s">
         <v>146</v>
       </c>
       <c r="B66" s="3">
@@ -8569,9 +8573,17 @@
         <f t="shared" si="8"/>
         <v>9298</v>
       </c>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" t="s">
+      <c r="AE66" s="2">
+        <f>AB66/AA66*1000</f>
+        <v>31.533943577051353</v>
+      </c>
+      <c r="AF66" s="2">
+        <f>AC66/AA66*1000</f>
+        <v>19.60172532286559</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="11" t="s">
         <v>65</v>
       </c>
       <c r="B67" s="10">
@@ -8665,8 +8677,16 @@
         <f t="shared" ref="AC67:AC106" si="17">L67+X67</f>
         <v>2264</v>
       </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AE67" s="2">
+        <f>AB67/AA67*1000</f>
+        <v>39.078084560064653</v>
+      </c>
+      <c r="AF67" s="2">
+        <f>AC67/AA67*1000</f>
+        <v>23.160414514132562</v>
+      </c>
+    </row>
+    <row r="68" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>147</v>
       </c>
@@ -8762,7 +8782,7 @@
         <v>64152</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -8858,7 +8878,7 @@
         <v>40290</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>149</v>
       </c>
@@ -8954,7 +8974,7 @@
         <v>2425135</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>150</v>
       </c>
@@ -9050,7 +9070,7 @@
         <v>96350</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>151</v>
       </c>
@@ -9146,7 +9166,7 @@
         <v>3460260</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>152</v>
       </c>
@@ -9242,7 +9262,7 @@
         <v>18960</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>153</v>
       </c>
@@ -9338,7 +9358,7 @@
         <v>14063</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>178</v>
       </c>
@@ -9434,7 +9454,7 @@
         <v>15597</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>154</v>
       </c>
@@ -9530,7 +9550,7 @@
         <v>5757</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>155</v>
       </c>
@@ -9626,7 +9646,7 @@
         <v>67195</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>156</v>
       </c>
@@ -9722,7 +9742,7 @@
         <v>17762</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -9818,7 +9838,7 @@
         <v>37635</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -16291,7 +16311,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93360861-95F9-4E60-AAA6-1A2501EF2A8B}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -16317,6 +16337,11 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
